--- a/00_Data/Seeds_data/X-ray_viability.xlsx
+++ b/00_Data/Seeds_data/X-ray_viability.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uq-my.sharepoint.com/personal/uqfchar1_uq_edu_au/Documents/Desktop/GitHub/Allocasuarina_germfire/00_Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uq-my.sharepoint.com/personal/uqfchar1_uq_edu_au/Documents/Desktop/GitHub/Allocasuarina_germfire/00_Data/Seeds_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{14DC5569-685B-A74D-B274-E270B2FEC4AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE41C4F3-1B4D-DA4E-8FE8-F8FF6531B339}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{14DC5569-685B-A74D-B274-E270B2FEC4AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{797F9634-EA72-B441-B61B-5BA38ADAF979}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="15860" activeTab="1" xr2:uid="{BCF8C07C-C135-E44A-B48B-EA5E6837DC43}"/>
   </bookViews>
@@ -660,6 +660,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Thermal_gradient_bar"/>
